--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K522"/>
+  <dimension ref="A1:K525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20802,6 +20802,123 @@
       <c r="K522" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:26:28+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>308.96</v>
+      </c>
+      <c r="C523" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D523" t="n">
+        <v>324.88</v>
+      </c>
+      <c r="E523" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="F523" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="G523" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="H523" t="n">
+        <v>327.23</v>
+      </c>
+      <c r="I523" t="n">
+        <v>321.79</v>
+      </c>
+      <c r="J523" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>310.76</v>
+      </c>
+      <c r="C524" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D524" t="n">
+        <v>324.88</v>
+      </c>
+      <c r="E524" t="n">
+        <v>321.74</v>
+      </c>
+      <c r="F524" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="G524" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="H524" t="n">
+        <v>327.23</v>
+      </c>
+      <c r="I524" t="n">
+        <v>321.79</v>
+      </c>
+      <c r="J524" t="n">
+        <v>319.86</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>310.8</v>
+      </c>
+      <c r="C525" t="n">
+        <v>312.02</v>
+      </c>
+      <c r="D525" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="E525" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="F525" t="n">
+        <v>321.64</v>
+      </c>
+      <c r="G525" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="H525" t="n">
+        <v>326.33</v>
+      </c>
+      <c r="I525" t="n">
+        <v>320.93</v>
+      </c>
+      <c r="J525" t="n">
+        <v>319.61</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20816,7 +20933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B580"/>
+  <dimension ref="A1:B583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26619,6 +26736,36 @@
       </c>
       <c r="B580" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -26787,28 +26934,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.482913188203343</v>
+        <v>-0.4821203595835634</v>
       </c>
       <c r="J2" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3556942910345259</v>
+        <v>0.3577162699967221</v>
       </c>
       <c r="M2" t="n">
-        <v>3.665893460637756</v>
+        <v>3.651347708543477</v>
       </c>
       <c r="N2" t="n">
-        <v>22.45484208285229</v>
+        <v>22.33302094594975</v>
       </c>
       <c r="O2" t="n">
-        <v>4.738654037050215</v>
+        <v>4.725782574976313</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5130024178188</v>
+        <v>322.5040488819951</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26865,28 +27012,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.350054057093675</v>
+        <v>-0.351527773105868</v>
       </c>
       <c r="J3" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2306816210676387</v>
+        <v>0.2343076123218666</v>
       </c>
       <c r="M3" t="n">
-        <v>3.289707070940224</v>
+        <v>3.277963774597413</v>
       </c>
       <c r="N3" t="n">
-        <v>21.8874104639801</v>
+        <v>21.7718301836969</v>
       </c>
       <c r="O3" t="n">
-        <v>4.678398279751319</v>
+        <v>4.666029380929453</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1014357054439</v>
+        <v>323.1179867545943</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26943,28 +27090,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4623544643013588</v>
+        <v>-0.4627576875671839</v>
       </c>
       <c r="J4" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3827004049497404</v>
+        <v>0.3854903677621648</v>
       </c>
       <c r="M4" t="n">
-        <v>3.344046096197301</v>
+        <v>3.33989403965761</v>
       </c>
       <c r="N4" t="n">
-        <v>18.46792998767182</v>
+        <v>18.40476046707216</v>
       </c>
       <c r="O4" t="n">
-        <v>4.297432953249162</v>
+        <v>4.290076976823628</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6187584032593</v>
+        <v>339.6232621271756</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27021,28 +27168,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5270380936205468</v>
+        <v>-0.5290271838380138</v>
       </c>
       <c r="J5" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4404643447720933</v>
+        <v>0.4451457344893461</v>
       </c>
       <c r="M5" t="n">
-        <v>3.595362968043536</v>
+        <v>3.583901497262457</v>
       </c>
       <c r="N5" t="n">
-        <v>18.89870558916355</v>
+        <v>18.80790452347862</v>
       </c>
       <c r="O5" t="n">
-        <v>4.347264149918147</v>
+        <v>4.336808103142059</v>
       </c>
       <c r="P5" t="n">
-        <v>337.8508256110297</v>
+        <v>337.8731600038839</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27099,28 +27246,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5212833372164422</v>
+        <v>-0.5231266391805081</v>
       </c>
       <c r="J6" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K6" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3886096251317624</v>
+        <v>0.3929749473257704</v>
       </c>
       <c r="M6" t="n">
-        <v>3.92416373832319</v>
+        <v>3.907443038842058</v>
       </c>
       <c r="N6" t="n">
-        <v>22.89727334114368</v>
+        <v>22.79098758489511</v>
       </c>
       <c r="O6" t="n">
-        <v>4.78510954327523</v>
+        <v>4.773990739925572</v>
       </c>
       <c r="P6" t="n">
-        <v>336.6659485221513</v>
+        <v>336.6866375025454</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27177,28 +27324,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4296195939566136</v>
+        <v>-0.4344222902797741</v>
       </c>
       <c r="J7" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2734797965457666</v>
+        <v>0.2796331834481063</v>
       </c>
       <c r="M7" t="n">
-        <v>3.836945476686862</v>
+        <v>3.831870850937344</v>
       </c>
       <c r="N7" t="n">
-        <v>26.26162809931144</v>
+        <v>26.2118041992053</v>
       </c>
       <c r="O7" t="n">
-        <v>5.124610043633705</v>
+        <v>5.119746497552911</v>
       </c>
       <c r="P7" t="n">
-        <v>344.5605661641801</v>
+        <v>344.6145004132052</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27255,28 +27402,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3136828143309218</v>
+        <v>-0.3183055439561424</v>
       </c>
       <c r="J8" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K8" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1809433940662201</v>
+        <v>0.1865960115159732</v>
       </c>
       <c r="M8" t="n">
-        <v>3.604422964278857</v>
+        <v>3.596955249367179</v>
       </c>
       <c r="N8" t="n">
-        <v>23.85523366971536</v>
+        <v>23.81222996670735</v>
       </c>
       <c r="O8" t="n">
-        <v>4.884181985728557</v>
+        <v>4.879777655458018</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4491703316079</v>
+        <v>339.5010845095487</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27333,28 +27480,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2601483999802829</v>
+        <v>-0.2645253487072342</v>
       </c>
       <c r="J9" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K9" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1268121905323211</v>
+        <v>0.1315773688102136</v>
       </c>
       <c r="M9" t="n">
-        <v>4.02632855321763</v>
+        <v>4.023871373740272</v>
       </c>
       <c r="N9" t="n">
-        <v>24.95858823441497</v>
+        <v>24.89959296272933</v>
       </c>
       <c r="O9" t="n">
-        <v>4.995857107085326</v>
+        <v>4.98994919440362</v>
       </c>
       <c r="P9" t="n">
-        <v>332.361316147968</v>
+        <v>332.4104701806662</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27411,28 +27558,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3138682194691406</v>
+        <v>-0.3173940040114107</v>
       </c>
       <c r="J10" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K10" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1278047977392593</v>
+        <v>0.1315517630104341</v>
       </c>
       <c r="M10" t="n">
-        <v>4.984864650479568</v>
+        <v>4.973578476508471</v>
       </c>
       <c r="N10" t="n">
-        <v>36.00744134481112</v>
+        <v>35.85522256405959</v>
       </c>
       <c r="O10" t="n">
-        <v>6.00062008002599</v>
+        <v>5.987923059296904</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3389835325713</v>
+        <v>331.3785769240006</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27470,7 +27617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K522"/>
+  <dimension ref="A1:K525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57223,6 +57370,177 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-01 22:26:28+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-46.61339689578926,168.83175630843238</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-46.61281599328051,168.83206795434256</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-46.612180644751284,168.8322834856437</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-46.611546678044704,168.8323484561083</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-46.61092557049817,168.83234916527405</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-46.61029755929339,168.83218342649369</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-46.609704723914014,168.83189983817022</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-46.60912263826522,168.83158182430282</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-46.608556654121095,168.83122513909294</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-46.61338999296324,168.83173507486103</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-46.61281599328051,168.83206795434256</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-46.612180644751284,168.8322834856437</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-46.611546678044704,168.8323484561083</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-46.610925571951235,168.83230977650945</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-46.61029755929339,168.83218342649369</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-46.609704723914014,168.83189983817022</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-46.60912263826522,168.83158182430282</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-46.608556654121095,168.83122513909294</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-46.61338983956707,168.83173460300392</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-46.61281798741728,168.8320740884306</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-46.61216778604303,168.8322112512171</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-46.61154656085636,168.83234298077792</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-46.610925571702005,168.83231655868076</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-46.610296602972234,168.8321925820895</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-46.60970193580463,168.83191085702816</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-46.609119628320954,168.8315921552969</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-46.60855577914282,168.83122814226027</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K525"/>
+  <dimension ref="A1:K528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20896,7 +20896,7 @@
         <v>312.02</v>
       </c>
       <c r="D525" t="n">
-        <v>330.6</v>
+        <v>324.88</v>
       </c>
       <c r="E525" t="n">
         <v>322.16</v>
@@ -20917,6 +20917,123 @@
         <v>319.61</v>
       </c>
       <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:32+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>309.52</v>
+      </c>
+      <c r="C526" t="n">
+        <v>311.31</v>
+      </c>
+      <c r="D526" t="n">
+        <v>324.78</v>
+      </c>
+      <c r="E526" t="n">
+        <v>320.74</v>
+      </c>
+      <c r="F526" t="n">
+        <v>321.64</v>
+      </c>
+      <c r="G526" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="H526" t="n">
+        <v>326.33</v>
+      </c>
+      <c r="I526" t="n">
+        <v>320.87</v>
+      </c>
+      <c r="J526" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="C527" t="n">
+        <v>311.31</v>
+      </c>
+      <c r="D527" t="n">
+        <v>324.78</v>
+      </c>
+      <c r="E527" t="n">
+        <v>320.74</v>
+      </c>
+      <c r="F527" t="n">
+        <v>321.64</v>
+      </c>
+      <c r="G527" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="H527" t="n">
+        <v>326.33</v>
+      </c>
+      <c r="I527" t="n">
+        <v>320.87</v>
+      </c>
+      <c r="J527" t="n">
+        <v>319.19</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>308.77</v>
+      </c>
+      <c r="C528" t="n">
+        <v>312.96</v>
+      </c>
+      <c r="D528" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="E528" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="F528" t="n">
+        <v>322.37</v>
+      </c>
+      <c r="G528" t="n">
+        <v>328.99</v>
+      </c>
+      <c r="H528" t="n">
+        <v>327.66</v>
+      </c>
+      <c r="I528" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="J528" t="n">
+        <v>319.09</v>
+      </c>
+      <c r="K528" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20933,7 +21050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26766,6 +26883,36 @@
       </c>
       <c r="B583" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -26934,28 +27081,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4821203595835634</v>
+        <v>-0.4829431151172043</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3577162699967221</v>
+        <v>0.3612703893271998</v>
       </c>
       <c r="M2" t="n">
-        <v>3.651347708543477</v>
+        <v>3.634308517967995</v>
       </c>
       <c r="N2" t="n">
-        <v>22.33302094594975</v>
+        <v>22.21098846796845</v>
       </c>
       <c r="O2" t="n">
-        <v>4.725782574976313</v>
+        <v>4.712853537716661</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5040488819951</v>
+        <v>322.5133600971035</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27012,28 +27159,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.351527773105868</v>
+        <v>-0.3534933280262755</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2343076123218666</v>
+        <v>0.2383544503962313</v>
       </c>
       <c r="M3" t="n">
-        <v>3.277963774597413</v>
+        <v>3.268695894127033</v>
       </c>
       <c r="N3" t="n">
-        <v>21.7718301836969</v>
+        <v>21.66847073040062</v>
       </c>
       <c r="O3" t="n">
-        <v>4.666029380929453</v>
+        <v>4.654940464753617</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1179867545943</v>
+        <v>323.1401115940517</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27090,28 +27237,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4627576875671839</v>
+        <v>-0.4672616120264285</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3854903677621648</v>
+        <v>0.3928594424619181</v>
       </c>
       <c r="M4" t="n">
-        <v>3.33989403965761</v>
+        <v>3.326730853578533</v>
       </c>
       <c r="N4" t="n">
-        <v>18.40476046707216</v>
+        <v>18.3108468737834</v>
       </c>
       <c r="O4" t="n">
-        <v>4.290076976823628</v>
+        <v>4.279117534467055</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6232621271756</v>
+        <v>339.6739301913921</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27168,28 +27315,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5290271838380138</v>
+        <v>-0.5318526450301683</v>
       </c>
       <c r="J5" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4451457344893461</v>
+        <v>0.4503208664973614</v>
       </c>
       <c r="M5" t="n">
-        <v>3.583901497262457</v>
+        <v>3.576335905692254</v>
       </c>
       <c r="N5" t="n">
-        <v>18.80790452347862</v>
+        <v>18.7372565113467</v>
       </c>
       <c r="O5" t="n">
-        <v>4.336808103142059</v>
+        <v>4.32865527749054</v>
       </c>
       <c r="P5" t="n">
-        <v>337.8731600038839</v>
+        <v>337.904969737973</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27246,28 +27393,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5231266391805081</v>
+        <v>-0.5238592383491573</v>
       </c>
       <c r="J6" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K6" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3929749473257704</v>
+        <v>0.3965313253937477</v>
       </c>
       <c r="M6" t="n">
-        <v>3.907443038842058</v>
+        <v>3.887449423773641</v>
       </c>
       <c r="N6" t="n">
-        <v>22.79098758489511</v>
+        <v>22.66431615796637</v>
       </c>
       <c r="O6" t="n">
-        <v>4.773990739925572</v>
+        <v>4.760705426506282</v>
       </c>
       <c r="P6" t="n">
-        <v>336.6866375025454</v>
+        <v>336.6948833586616</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27324,28 +27471,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4344222902797741</v>
+        <v>-0.4393148320392721</v>
       </c>
       <c r="J7" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K7" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2796331834481063</v>
+        <v>0.2858282043053577</v>
       </c>
       <c r="M7" t="n">
-        <v>3.831870850937344</v>
+        <v>3.827198920700077</v>
       </c>
       <c r="N7" t="n">
-        <v>26.2118041992053</v>
+        <v>26.1689032722067</v>
       </c>
       <c r="O7" t="n">
-        <v>5.119746497552911</v>
+        <v>5.115555030708467</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6145004132052</v>
+        <v>344.6695855341799</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27402,28 +27549,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3183055439561424</v>
+        <v>-0.3229402772494682</v>
       </c>
       <c r="J8" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K8" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1865960115159732</v>
+        <v>0.1922830678898496</v>
       </c>
       <c r="M8" t="n">
-        <v>3.596955249367179</v>
+        <v>3.58962947342254</v>
       </c>
       <c r="N8" t="n">
-        <v>23.81222996670735</v>
+        <v>23.77380782257796</v>
       </c>
       <c r="O8" t="n">
-        <v>4.879777655458018</v>
+        <v>4.875839191624141</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5010845095487</v>
+        <v>339.5532643879502</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27480,28 +27627,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2645253487072342</v>
+        <v>-0.269265959221884</v>
       </c>
       <c r="J9" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K9" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1315773688102136</v>
+        <v>0.1366555285928358</v>
       </c>
       <c r="M9" t="n">
-        <v>4.023871373740272</v>
+        <v>4.023307852651454</v>
       </c>
       <c r="N9" t="n">
-        <v>24.89959296272933</v>
+        <v>24.85741642228633</v>
       </c>
       <c r="O9" t="n">
-        <v>4.98994919440362</v>
+        <v>4.985721253969813</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4104701806662</v>
+        <v>332.4638453098438</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27558,28 +27705,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3173940040114107</v>
+        <v>-0.3214916955028062</v>
       </c>
       <c r="J10" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K10" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1315517630104341</v>
+        <v>0.1356960596144405</v>
       </c>
       <c r="M10" t="n">
-        <v>4.973578476508471</v>
+        <v>4.965100037028525</v>
       </c>
       <c r="N10" t="n">
-        <v>35.85522256405959</v>
+        <v>35.72522315626811</v>
       </c>
       <c r="O10" t="n">
-        <v>5.987923059296904</v>
+        <v>5.977058068671252</v>
       </c>
       <c r="P10" t="n">
-        <v>331.3785769240006</v>
+        <v>331.4247155037885</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27617,7 +27764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K525"/>
+  <dimension ref="A1:K528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57502,7 +57649,7 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>-46.61216778604303,168.8322112512171</t>
+          <t>-46.612180644751284,168.8322834856437</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
@@ -57536,6 +57683,177 @@
         </is>
       </c>
       <c r="K525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:32+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-46.6133947482438,168.83174970243178</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-46.61282071018043,168.8320824638208</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-46.612180869553484,168.83228474848366</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-46.6115469570635,168.8323614926093</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-46.610925571702005,168.83231655868076</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-46.610296602972234,168.8321925820895</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-46.60970193580463,168.83191085702816</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-46.6091194183248,168.8315928760639</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-46.60855430917917,168.83123318758118</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-02 22:26:46+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-46.61340088408703,168.8317685767206</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-46.61282071018043,168.8320824638208</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-46.612180869553484,168.83228474848366</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-46.6115469570635,168.8323614926093</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-46.610925571702005,168.83231655868076</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-46.610296602972234,168.8321925820895</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-46.60970193580463,168.83191085702816</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-46.6091194183248,168.8315928760639</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-46.60855430917917,168.83123318758118</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-46.613397624420685,168.83175854975414</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-46.61281438263135,168.8320629998872</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-46.6121793633785,168.83227628745615</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-46.61154669478588,168.83234923829832</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-46.610925572051755,168.83230703755567</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-46.61029755929339,168.83218342649369</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-46.60970605601034,168.83189457360436</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-46.609121273290626,168.83158650928866</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-46.60855395918777,168.831234388848</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0553/nzd0553.xlsx
+++ b/data/nzd0553/nzd0553.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K528"/>
+  <dimension ref="A1:K529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21034,6 +21034,45 @@
         <v>319.09</v>
       </c>
       <c r="K528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>308.07</v>
+      </c>
+      <c r="C529" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D529" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="E529" t="n">
+        <v>320.92</v>
+      </c>
+      <c r="F529" t="n">
+        <v>320.97</v>
+      </c>
+      <c r="G529" t="n">
+        <v>326.39</v>
+      </c>
+      <c r="H529" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="I529" t="n">
+        <v>318.93</v>
+      </c>
+      <c r="J529" t="n">
+        <v>315.66</v>
+      </c>
+      <c r="K529" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21050,7 +21089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26913,6 +26952,16 @@
       </c>
       <c r="B586" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -27081,28 +27130,28 @@
         <v>0.0541</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4829431151172043</v>
+        <v>-0.4834505770600013</v>
       </c>
       <c r="J2" t="n">
+        <v>528</v>
+      </c>
+      <c r="K2" t="n">
         <v>527</v>
       </c>
-      <c r="K2" t="n">
-        <v>526</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3612703893271998</v>
+        <v>0.3626653907861592</v>
       </c>
       <c r="M2" t="n">
-        <v>3.634308517967995</v>
+        <v>3.6296307689097</v>
       </c>
       <c r="N2" t="n">
-        <v>22.21098846796845</v>
+        <v>22.17223191995772</v>
       </c>
       <c r="O2" t="n">
-        <v>4.712853537716661</v>
+        <v>4.708739950343161</v>
       </c>
       <c r="P2" t="n">
-        <v>322.5133600971035</v>
+        <v>322.5191227531348</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27159,28 +27208,28 @@
         <v>0.0765</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3534933280262755</v>
+        <v>-0.3538728116503049</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2383544503962313</v>
+        <v>0.2394700506070955</v>
       </c>
       <c r="M3" t="n">
-        <v>3.268695894127033</v>
+        <v>3.264298332402674</v>
       </c>
       <c r="N3" t="n">
-        <v>21.66847073040062</v>
+        <v>21.62934857363662</v>
       </c>
       <c r="O3" t="n">
-        <v>4.654940464753617</v>
+        <v>4.650736347465487</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1401115940517</v>
+        <v>323.1444004410814</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27237,28 +27286,28 @@
         <v>0.0696</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4672616120264285</v>
+        <v>-0.4678417882608195</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3928594424619181</v>
+        <v>0.3943666434950037</v>
       </c>
       <c r="M4" t="n">
-        <v>3.326730853578533</v>
+        <v>3.322847391145965</v>
       </c>
       <c r="N4" t="n">
-        <v>18.3108468737834</v>
+        <v>18.28064713983568</v>
       </c>
       <c r="O4" t="n">
-        <v>4.279117534467055</v>
+        <v>4.275587344428327</v>
       </c>
       <c r="P4" t="n">
-        <v>339.6739301913921</v>
+        <v>339.6804872256408</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27315,28 +27364,28 @@
         <v>0.0868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5318526450301683</v>
+        <v>-0.5328140964760425</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4503208664973614</v>
+        <v>0.4520622648718243</v>
       </c>
       <c r="M5" t="n">
-        <v>3.576335905692254</v>
+        <v>3.573893788451923</v>
       </c>
       <c r="N5" t="n">
-        <v>18.7372565113467</v>
+        <v>18.71407206121235</v>
       </c>
       <c r="O5" t="n">
-        <v>4.32865527749054</v>
+        <v>4.325976428647335</v>
       </c>
       <c r="P5" t="n">
-        <v>337.904969737973</v>
+        <v>337.9158358674097</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27393,28 +27442,28 @@
         <v>0.0866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5238592383491573</v>
+        <v>-0.5244272653408064</v>
       </c>
       <c r="J6" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K6" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3965313253937477</v>
+        <v>0.3979813138063306</v>
       </c>
       <c r="M6" t="n">
-        <v>3.887449423773641</v>
+        <v>3.881804650559896</v>
       </c>
       <c r="N6" t="n">
-        <v>22.66431615796637</v>
+        <v>22.62568555785182</v>
       </c>
       <c r="O6" t="n">
-        <v>4.760705426506282</v>
+        <v>4.756646461305677</v>
       </c>
       <c r="P6" t="n">
-        <v>336.6948833586616</v>
+        <v>336.7013030846305</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27471,28 +27520,28 @@
         <v>0.0736</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4393148320392721</v>
+        <v>-0.4417066719216945</v>
       </c>
       <c r="J7" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K7" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2858282043053577</v>
+        <v>0.2882895103114484</v>
       </c>
       <c r="M7" t="n">
-        <v>3.827198920700077</v>
+        <v>3.828230787831432</v>
       </c>
       <c r="N7" t="n">
-        <v>26.1689032722067</v>
+        <v>26.19548092231782</v>
       </c>
       <c r="O7" t="n">
-        <v>5.115555030708467</v>
+        <v>5.118152100350068</v>
       </c>
       <c r="P7" t="n">
-        <v>344.6695855341799</v>
+        <v>344.6966176239084</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27549,28 +27598,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3229402772494682</v>
+        <v>-0.3250948217229623</v>
       </c>
       <c r="J8" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K8" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1922830678898496</v>
+        <v>0.194588487630643</v>
       </c>
       <c r="M8" t="n">
-        <v>3.58962947342254</v>
+        <v>3.588938970655733</v>
       </c>
       <c r="N8" t="n">
-        <v>23.77380782257796</v>
+        <v>23.79056330728148</v>
       </c>
       <c r="O8" t="n">
-        <v>4.875839191624141</v>
+        <v>4.877557104461359</v>
       </c>
       <c r="P8" t="n">
-        <v>339.5532643879502</v>
+        <v>339.5776146130466</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27627,28 +27676,28 @@
         <v>0.0692</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.269265959221884</v>
+        <v>-0.2716063889473427</v>
       </c>
       <c r="J9" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K9" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1366555285928358</v>
+        <v>0.1388472157905857</v>
       </c>
       <c r="M9" t="n">
-        <v>4.023307852651454</v>
+        <v>4.026686913494724</v>
       </c>
       <c r="N9" t="n">
-        <v>24.85741642228633</v>
+        <v>24.88324002324961</v>
       </c>
       <c r="O9" t="n">
-        <v>4.985721253969813</v>
+        <v>4.988310337504034</v>
       </c>
       <c r="P9" t="n">
-        <v>332.4638453098438</v>
+        <v>332.4902963723949</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27705,28 +27754,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3214916955028062</v>
+        <v>-0.324138122357892</v>
       </c>
       <c r="J10" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K10" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1356960596144405</v>
+        <v>0.1378047930305858</v>
       </c>
       <c r="M10" t="n">
-        <v>4.965100037028525</v>
+        <v>4.968441263702257</v>
       </c>
       <c r="N10" t="n">
-        <v>35.72522315626811</v>
+        <v>35.75077298487628</v>
       </c>
       <c r="O10" t="n">
-        <v>5.977058068671252</v>
+        <v>5.979195011443955</v>
       </c>
       <c r="P10" t="n">
-        <v>331.4247155037885</v>
+        <v>331.454624883899</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27764,7 +27813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K528"/>
+  <dimension ref="A1:K529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57859,6 +57908,63 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-46.61340030885184,168.83176680725586</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-46.61281599328051,168.83206795434256</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-46.6121793633785,168.83227628745615</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-46.61154690684024,168.8323591460391</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-46.61092557138029,168.8323252972477</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-46.610294057268625,168.8322169540264</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-46.609698001470626,168.83192640585924</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-46.60911262844678,168.8316161808603</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-46.608541954475335,168.83127559229166</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
